--- a/Test_Results/Excel/Selenium_Report.xlsx
+++ b/Test_Results/Excel/Selenium_Report.xlsx
@@ -448,6 +448,8764 @@
 </a:theme>
 </file>
 
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G301"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>S.No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Test Suite</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Duration (ms)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Error Details</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Timestamp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TC-SEL-001: Verify Login Flow - scenario 1</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:39.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TC-SEL-002: Verify Dashboard - scenario 1</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>972</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:40.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TC-SEL-003: Verify Checkout - scenario 1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>900</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TC-SEL-004: Verify Product Search - scenario 1</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>518</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TC-SEL-005: Verify Settings - scenario 1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>258</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:42.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TC-SEL-006: Verify Registration - scenario 1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>760</v>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:43.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TC-SEL-007: Verify Login Flow - scenario 2</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>940</v>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:44.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TC-SEL-008: Verify Dashboard - scenario 2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>445</v>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TC-SEL-009: Verify Checkout - scenario 2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>774</v>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TC-SEL-010: Verify Product Search - scenario 2</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>723</v>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:46.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TC-SEL-011: Verify Settings - scenario 2</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>672</v>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:47.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TC-SEL-012: Verify Registration - scenario 2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1116</v>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:48.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TC-SEL-013: Verify Login Flow - scenario 3</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>479</v>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TC-SEL-014: Verify Dashboard - scenario 3</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>183</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TC-SEL-015: Verify Checkout - scenario 3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:50.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TC-SEL-016: Verify Product Search - scenario 3</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>519</v>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:51.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TC-SEL-017: Verify Settings - scenario 3</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>443</v>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:52.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TC-SEL-018: Verify Registration - scenario 3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>601</v>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TC-SEL-019: Verify Login Flow - scenario 4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>1041</v>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TC-SEL-020: Verify Dashboard - scenario 4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>715</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:54.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TC-SEL-021: Verify Checkout - scenario 4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>824</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:55.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TC-SEL-022: Verify Product Search - scenario 4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>427</v>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:56.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TC-SEL-023: Verify Settings - scenario 4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>904</v>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TC-SEL-024: Verify Registration - scenario 4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>139</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TC-SEL-025: Verify Login Flow - scenario 5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>199</v>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:58.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TC-SEL-026: Verify Dashboard - scenario 5</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>628</v>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:38:59.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TC-SEL-027: Verify Checkout - scenario 5</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>451</v>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TC-SEL-028: Verify Product Search - scenario 5</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>708</v>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TC-SEL-029: Verify Settings - scenario 5</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>697</v>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TC-SEL-030: Verify Registration - scenario 5</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>390</v>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:02.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TC-SEL-031: Verify Login Flow - scenario 6</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>662</v>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:03.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TC-SEL-032: Verify Dashboard - scenario 6</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>681</v>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:04.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TC-SEL-033: Verify Checkout - scenario 6</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>211</v>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TC-SEL-034: Verify Product Search - scenario 6</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1161</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TC-SEL-035: Verify Settings - scenario 6</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>805</v>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:06.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TC-SEL-036: Verify Registration - scenario 6</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>269</v>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:07.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TC-SEL-037: Verify Login Flow - scenario 7</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>509</v>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:08.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TC-SEL-038: Verify Dashboard - scenario 7</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TC-SEL-039: Verify Checkout - scenario 7</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>534</v>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TC-SEL-040: Verify Product Search - scenario 7</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>731</v>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:10.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TC-SEL-041: Verify Settings - scenario 7</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>1055</v>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:11.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TC-SEL-042: Verify Registration - scenario 7</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>997</v>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:12.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>TC-SEL-043: Verify Login Flow - scenario 8</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>111</v>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>TC-SEL-044: Verify Dashboard - scenario 8</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>260</v>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>TC-SEL-045: Verify Checkout - scenario 8</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>428</v>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:14.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TC-SEL-046: Verify Product Search - scenario 8</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>1198</v>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:15.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>TC-SEL-047: Verify Settings - scenario 8</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:16.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TC-SEL-048: Verify Registration - scenario 8</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>151</v>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>TC-SEL-049: Verify Login Flow - scenario 9</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>998</v>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>TC-SEL-050: Verify Dashboard - scenario 9</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>735</v>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:18.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TC-SEL-051: Verify Checkout - scenario 9</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>256</v>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:19.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TC-SEL-052: Verify Product Search - scenario 9</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>1154</v>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:20.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>TC-SEL-053: Verify Settings - scenario 9</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>348</v>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>TC-SEL-054: Verify Registration - scenario 9</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>1199</v>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>TC-SEL-055: Verify Login Flow - scenario 10</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>437</v>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:22.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>TC-SEL-056: Verify Dashboard - scenario 10</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>698</v>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:23.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>TC-SEL-057: Verify Checkout - scenario 10</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>772</v>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:24.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>TC-SEL-058: Verify Product Search - scenario 10</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>940</v>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>TC-SEL-059: Verify Settings - scenario 10</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>754</v>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>TC-SEL-060: Verify Registration - scenario 10</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>698</v>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:26.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>TC-SEL-061: Verify Login Flow - scenario 11</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>1150</v>
+      </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:27.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>TC-SEL-062: Verify Dashboard - scenario 11</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>112</v>
+      </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:28.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>TC-SEL-063: Verify Checkout - scenario 11</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>588</v>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>TC-SEL-064: Verify Product Search - scenario 11</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>1042</v>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>TC-SEL-065: Verify Settings - scenario 11</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>206</v>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:30.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>TC-SEL-066: Verify Registration - scenario 11</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>129</v>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:31.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>TC-SEL-067: Verify Login Flow - scenario 12</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>632</v>
+      </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:32.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>TC-SEL-068: Verify Dashboard - scenario 12</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>1189</v>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>69</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>TC-SEL-069: Verify Checkout - scenario 12</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>188</v>
+      </c>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>TC-SEL-070: Verify Product Search - scenario 12</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>309</v>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:34.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TC-SEL-071: Verify Settings - scenario 12</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:35.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>TC-SEL-072: Verify Registration - scenario 12</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>1128</v>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:36.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>TC-SEL-073: Verify Login Flow - scenario 13</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>607</v>
+      </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>TC-SEL-074: Verify Dashboard - scenario 13</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>375</v>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>TC-SEL-075: Verify Checkout - scenario 13</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>1049</v>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:38.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TC-SEL-076: Verify Product Search - scenario 13</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>719</v>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:39.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>TC-SEL-077: Verify Settings - scenario 13</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>443</v>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:40.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>TC-SEL-078: Verify Registration - scenario 13</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>613</v>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TC-SEL-079: Verify Login Flow - scenario 14</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>569</v>
+      </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>TC-SEL-080: Verify Dashboard - scenario 14</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>1187</v>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:42.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>TC-SEL-081: Verify Checkout - scenario 14</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>347</v>
+      </c>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:43.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>TC-SEL-082: Verify Product Search - scenario 14</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>470</v>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:44.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>TC-SEL-083: Verify Settings - scenario 14</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>1176</v>
+      </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>TC-SEL-084: Verify Registration - scenario 14</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>173</v>
+      </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TC-SEL-085: Verify Login Flow - scenario 15</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>1172</v>
+      </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:46.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>TC-SEL-086: Verify Dashboard - scenario 15</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>995</v>
+      </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:47.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>TC-SEL-087: Verify Checkout - scenario 15</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>434</v>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:48.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TC-SEL-088: Verify Product Search - scenario 15</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>TC-SEL-089: Verify Settings - scenario 15</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>727</v>
+      </c>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>TC-SEL-090: Verify Registration - scenario 15</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>916</v>
+      </c>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:50.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>TC-SEL-091: Verify Login Flow - scenario 16</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>290</v>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:51.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TC-SEL-092: Verify Dashboard - scenario 16</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1097</v>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:52.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>TC-SEL-093: Verify Checkout - scenario 16</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>387</v>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>TC-SEL-094: Verify Product Search - scenario 16</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>163</v>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TC-SEL-095: Verify Settings - scenario 16</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>1062</v>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:54.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>TC-SEL-096: Verify Registration - scenario 16</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:55.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>TC-SEL-097: Verify Login Flow - scenario 17</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1094</v>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:56.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>TC-SEL-098: Verify Dashboard - scenario 17</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>621</v>
+      </c>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>TC-SEL-099: Verify Checkout - scenario 17</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>635</v>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>TC-SEL-100: Verify Product Search - scenario 17</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>211</v>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:58.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>TC-SEL-101: Verify Settings - scenario 17</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>81</v>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:39:59.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>TC-SEL-102: Verify Registration - scenario 17</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>446</v>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>TC-SEL-103: Verify Login Flow - scenario 18</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>794</v>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>TC-SEL-104: Verify Dashboard - scenario 18</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>560</v>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>TC-SEL-105: Verify Checkout - scenario 18</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>181</v>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:02.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>TC-SEL-106: Verify Product Search - scenario 18</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>586</v>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:03.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>TC-SEL-107: Verify Settings - scenario 18</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>1152</v>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:04.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>TC-SEL-108: Verify Registration - scenario 18</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>1098</v>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>TC-SEL-109: Verify Login Flow - scenario 19</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>927</v>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TC-SEL-110: Verify Dashboard - scenario 19</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>935</v>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:06.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>TC-SEL-111: Verify Checkout - scenario 19</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>628</v>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:07.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TC-SEL-112: Verify Product Search - scenario 19</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>101</v>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:08.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>TC-SEL-113: Verify Settings - scenario 19</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>117</v>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>TC-SEL-114: Verify Registration - scenario 19</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>642</v>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>TC-SEL-115: Verify Login Flow - scenario 20</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>210</v>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:10.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>TC-SEL-116: Verify Dashboard - scenario 20</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1095</v>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:11.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>TC-SEL-117: Verify Checkout - scenario 20</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>1075</v>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:12.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>TC-SEL-118: Verify Product Search - scenario 20</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>TC-SEL-119: Verify Settings - scenario 20</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>256</v>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>TC-SEL-120: Verify Registration - scenario 20</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>167</v>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:14.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TC-SEL-121: Verify Login Flow - scenario 21</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>439</v>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:15.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>TC-SEL-122: Verify Dashboard - scenario 21</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>135</v>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:16.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>TC-SEL-123: Verify Checkout - scenario 21</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>646</v>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>TC-SEL-124: Verify Product Search - scenario 21</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>425</v>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>TC-SEL-125: Verify Settings - scenario 21</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>739</v>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:18.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>TC-SEL-126: Verify Registration - scenario 21</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>936</v>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:19.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>TC-SEL-127: Verify Login Flow - scenario 22</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>248</v>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:20.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>TC-SEL-128: Verify Dashboard - scenario 22</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>620</v>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>TC-SEL-129: Verify Checkout - scenario 22</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>154</v>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>TC-SEL-130: Verify Product Search - scenario 22</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>581</v>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:22.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>TC-SEL-131: Verify Settings - scenario 22</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>449</v>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:23.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>TC-SEL-132: Verify Registration - scenario 22</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>1052</v>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:24.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TC-SEL-133: Verify Login Flow - scenario 23</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>838</v>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>TC-SEL-134: Verify Dashboard - scenario 23</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>1129</v>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TC-SEL-135: Verify Checkout - scenario 23</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>979</v>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:26.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TC-SEL-136: Verify Product Search - scenario 23</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>838</v>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:27.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>TC-SEL-137: Verify Settings - scenario 23</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>757</v>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:28.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>TC-SEL-138: Verify Registration - scenario 23</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>956</v>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>TC-SEL-139: Verify Login Flow - scenario 24</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>645</v>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>TC-SEL-140: Verify Dashboard - scenario 24</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>410</v>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:30.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>TC-SEL-141: Verify Checkout - scenario 24</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>767</v>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:31.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TC-SEL-142: Verify Product Search - scenario 24</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>1119</v>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:32.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TC-SEL-143: Verify Settings - scenario 24</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>284</v>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>TC-SEL-144: Verify Registration - scenario 24</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>380</v>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TC-SEL-145: Verify Login Flow - scenario 25</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>670</v>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:34.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>TC-SEL-146: Verify Dashboard - scenario 25</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>597</v>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:35.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TC-SEL-147: Verify Checkout - scenario 25</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>159</v>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:36.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>TC-SEL-148: Verify Product Search - scenario 25</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>266</v>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TC-SEL-149: Verify Settings - scenario 25</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>1142</v>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>TC-SEL-150: Verify Registration - scenario 25</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>1122</v>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:38.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>TC-SEL-151: Verify Login Flow - scenario 26</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>814</v>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:39.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>TC-SEL-152: Verify Dashboard - scenario 26</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>1114</v>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:40.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TC-SEL-153: Verify Checkout - scenario 26</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>252</v>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TC-SEL-154: Verify Product Search - scenario 26</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1084</v>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>TC-SEL-155: Verify Settings - scenario 26</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>981</v>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:42.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>TC-SEL-156: Verify Registration - scenario 26</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1157</v>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:43.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>TC-SEL-157: Verify Login Flow - scenario 27</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>235</v>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:44.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>TC-SEL-158: Verify Dashboard - scenario 27</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>146</v>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>TC-SEL-159: Verify Checkout - scenario 27</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>503</v>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>TC-SEL-160: Verify Product Search - scenario 27</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>530</v>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:46.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>TC-SEL-161: Verify Settings - scenario 27</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>554</v>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:47.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>TC-SEL-162: Verify Registration - scenario 27</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>628</v>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:48.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>TC-SEL-163: Verify Login Flow - scenario 28</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>811</v>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>TC-SEL-164: Verify Dashboard - scenario 28</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>TC-SEL-165: Verify Checkout - scenario 28</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>903</v>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:50.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>TC-SEL-166: Verify Product Search - scenario 28</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>863</v>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:51.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>TC-SEL-167: Verify Settings - scenario 28</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>771</v>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:52.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>TC-SEL-168: Verify Registration - scenario 28</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>823</v>
+      </c>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>169</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>TC-SEL-169: Verify Login Flow - scenario 29</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>1030</v>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>170</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>TC-SEL-170: Verify Dashboard - scenario 29</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>496</v>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:54.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>171</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>TC-SEL-171: Verify Checkout - scenario 29</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>751</v>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:55.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>172</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>TC-SEL-172: Verify Product Search - scenario 29</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>285</v>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:56.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>173</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>TC-SEL-173: Verify Settings - scenario 29</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>833</v>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>174</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>TC-SEL-174: Verify Registration - scenario 29</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>334</v>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>175</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>TC-SEL-175: Verify Login Flow - scenario 30</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>392</v>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:58.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>176</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>TC-SEL-176: Verify Dashboard - scenario 30</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>1160</v>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:40:59.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>177</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>TC-SEL-177: Verify Checkout - scenario 30</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>122</v>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>178</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>TC-SEL-178: Verify Product Search - scenario 30</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>508</v>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>179</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>TC-SEL-179: Verify Settings - scenario 30</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>429</v>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>180</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>TC-SEL-180: Verify Registration - scenario 30</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>540</v>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:02.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>TC-SEL-181: Verify Login Flow - scenario 31</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>206</v>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:03.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>TC-SEL-182: Verify Dashboard - scenario 31</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>123</v>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:04.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>TC-SEL-183: Verify Checkout - scenario 31</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>693</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>184</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>TC-SEL-184: Verify Product Search - scenario 31</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>580</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>185</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>TC-SEL-185: Verify Settings - scenario 31</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>868</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:06.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>186</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>TC-SEL-186: Verify Registration - scenario 31</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>1076</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:07.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>187</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>TC-SEL-187: Verify Login Flow - scenario 32</t>
+        </is>
+      </c>
+      <c r="D188" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>286</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:08.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>TC-SEL-188: Verify Dashboard - scenario 32</t>
+        </is>
+      </c>
+      <c r="D189" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>777</v>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>189</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>TC-SEL-189: Verify Checkout - scenario 32</t>
+        </is>
+      </c>
+      <c r="D190" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>427</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>190</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>TC-SEL-190: Verify Product Search - scenario 32</t>
+        </is>
+      </c>
+      <c r="D191" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>364</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:10.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>191</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>TC-SEL-191: Verify Settings - scenario 32</t>
+        </is>
+      </c>
+      <c r="D192" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>828</v>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:11.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>192</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>TC-SEL-192: Verify Registration - scenario 32</t>
+        </is>
+      </c>
+      <c r="D193" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>455</v>
+      </c>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:12.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>193</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>TC-SEL-193: Verify Login Flow - scenario 33</t>
+        </is>
+      </c>
+      <c r="D194" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>704</v>
+      </c>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>194</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>TC-SEL-194: Verify Dashboard - scenario 33</t>
+        </is>
+      </c>
+      <c r="D195" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>201</v>
+      </c>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>195</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>TC-SEL-195: Verify Checkout - scenario 33</t>
+        </is>
+      </c>
+      <c r="D196" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>372</v>
+      </c>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:14.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>196</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>TC-SEL-196: Verify Product Search - scenario 33</t>
+        </is>
+      </c>
+      <c r="D197" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>267</v>
+      </c>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:15.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>197</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>TC-SEL-197: Verify Settings - scenario 33</t>
+        </is>
+      </c>
+      <c r="D198" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>185</v>
+      </c>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:16.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>198</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>TC-SEL-198: Verify Registration - scenario 33</t>
+        </is>
+      </c>
+      <c r="D199" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>116</v>
+      </c>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>199</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>TC-SEL-199: Verify Login Flow - scenario 34</t>
+        </is>
+      </c>
+      <c r="D200" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>830</v>
+      </c>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>200</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>TC-SEL-200: Verify Dashboard - scenario 34</t>
+        </is>
+      </c>
+      <c r="D201" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>1064</v>
+      </c>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:18.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>201</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>TC-SEL-201: Verify Checkout - scenario 34</t>
+        </is>
+      </c>
+      <c r="D202" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>495</v>
+      </c>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:19.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>202</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>TC-SEL-202: Verify Product Search - scenario 34</t>
+        </is>
+      </c>
+      <c r="D203" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>780</v>
+      </c>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:20.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>203</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>TC-SEL-203: Verify Settings - scenario 34</t>
+        </is>
+      </c>
+      <c r="D204" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>262</v>
+      </c>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>204</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>TC-SEL-204: Verify Registration - scenario 34</t>
+        </is>
+      </c>
+      <c r="D205" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>122</v>
+      </c>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>205</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>TC-SEL-205: Verify Login Flow - scenario 35</t>
+        </is>
+      </c>
+      <c r="D206" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>813</v>
+      </c>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:22.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>206</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>TC-SEL-206: Verify Dashboard - scenario 35</t>
+        </is>
+      </c>
+      <c r="D207" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>855</v>
+      </c>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:23.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>207</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>TC-SEL-207: Verify Checkout - scenario 35</t>
+        </is>
+      </c>
+      <c r="D208" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>88</v>
+      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:24.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>208</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>TC-SEL-208: Verify Product Search - scenario 35</t>
+        </is>
+      </c>
+      <c r="D209" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>318</v>
+      </c>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>209</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>TC-SEL-209: Verify Settings - scenario 35</t>
+        </is>
+      </c>
+      <c r="D210" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>888</v>
+      </c>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>210</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>TC-SEL-210: Verify Registration - scenario 35</t>
+        </is>
+      </c>
+      <c r="D211" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E211" t="n">
+        <v>702</v>
+      </c>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:26.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>211</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>TC-SEL-211: Verify Login Flow - scenario 36</t>
+        </is>
+      </c>
+      <c r="D212" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E212" t="n">
+        <v>135</v>
+      </c>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:27.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>212</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>TC-SEL-212: Verify Dashboard - scenario 36</t>
+        </is>
+      </c>
+      <c r="D213" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E213" t="n">
+        <v>193</v>
+      </c>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:28.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>TC-SEL-213: Verify Checkout - scenario 36</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E214" t="n">
+        <v>988</v>
+      </c>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>TC-SEL-214: Verify Product Search - scenario 36</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E215" t="n">
+        <v>1137</v>
+      </c>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>TC-SEL-215: Verify Settings - scenario 36</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E216" t="n">
+        <v>852</v>
+      </c>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:30.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>TC-SEL-216: Verify Registration - scenario 36</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E217" t="n">
+        <v>267</v>
+      </c>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:31.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>TC-SEL-217: Verify Login Flow - scenario 37</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E218" t="n">
+        <v>725</v>
+      </c>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:32.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>TC-SEL-218: Verify Dashboard - scenario 37</t>
+        </is>
+      </c>
+      <c r="D219" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E219" t="n">
+        <v>582</v>
+      </c>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>TC-SEL-219: Verify Checkout - scenario 37</t>
+        </is>
+      </c>
+      <c r="D220" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E220" t="n">
+        <v>937</v>
+      </c>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>TC-SEL-220: Verify Product Search - scenario 37</t>
+        </is>
+      </c>
+      <c r="D221" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E221" t="n">
+        <v>165</v>
+      </c>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:34.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>TC-SEL-221: Verify Settings - scenario 37</t>
+        </is>
+      </c>
+      <c r="D222" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E222" t="n">
+        <v>919</v>
+      </c>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:35.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>TC-SEL-222: Verify Registration - scenario 37</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E223" t="n">
+        <v>229</v>
+      </c>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:36.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>TC-SEL-223: Verify Login Flow - scenario 38</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E224" t="n">
+        <v>167</v>
+      </c>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>224</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>TC-SEL-224: Verify Dashboard - scenario 38</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E225" t="n">
+        <v>493</v>
+      </c>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>225</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>TC-SEL-225: Verify Checkout - scenario 38</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E226" t="n">
+        <v>670</v>
+      </c>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:38.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>226</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>TC-SEL-226: Verify Product Search - scenario 38</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E227" t="n">
+        <v>937</v>
+      </c>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:39.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>227</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>TC-SEL-227: Verify Settings - scenario 38</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E228" t="n">
+        <v>438</v>
+      </c>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:40.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>228</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>TC-SEL-228: Verify Registration - scenario 38</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>463</v>
+      </c>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>229</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>TC-SEL-229: Verify Login Flow - scenario 39</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>1176</v>
+      </c>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:41.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>230</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>TC-SEL-230: Verify Dashboard - scenario 39</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E231" t="n">
+        <v>1174</v>
+      </c>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:42.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>231</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>TC-SEL-231: Verify Checkout - scenario 39</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>543</v>
+      </c>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:43.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>232</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>TC-SEL-232: Verify Product Search - scenario 39</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>936</v>
+      </c>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:44.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>233</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>TC-SEL-233: Verify Settings - scenario 39</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>470</v>
+      </c>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>234</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>TC-SEL-234: Verify Registration - scenario 39</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>936</v>
+      </c>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:45.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>235</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>TC-SEL-235: Verify Login Flow - scenario 40</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>148</v>
+      </c>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:46.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>236</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>TC-SEL-236: Verify Dashboard - scenario 40</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>118</v>
+      </c>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:47.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>237</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>TC-SEL-237: Verify Checkout - scenario 40</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>647</v>
+      </c>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:48.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>238</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>TC-SEL-238: Verify Product Search - scenario 40</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>761</v>
+      </c>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>239</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>TC-SEL-239: Verify Settings - scenario 40</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>1133</v>
+      </c>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:49.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>240</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>TC-SEL-240: Verify Registration - scenario 40</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>425</v>
+      </c>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:50.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>241</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>TC-SEL-241: Verify Login Flow - scenario 41</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>747</v>
+      </c>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:51.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>242</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>TC-SEL-242: Verify Dashboard - scenario 41</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>80</v>
+      </c>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:52.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>243</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>TC-SEL-243: Verify Checkout - scenario 41</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>312</v>
+      </c>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>244</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>TC-SEL-244: Verify Product Search - scenario 41</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>915</v>
+      </c>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:53.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>245</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>TC-SEL-245: Verify Settings - scenario 41</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>278</v>
+      </c>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:54.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>246</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>TC-SEL-246: Verify Registration - scenario 41</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>287</v>
+      </c>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:55.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>247</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>TC-SEL-247: Verify Login Flow - scenario 42</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>1134</v>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:56.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>248</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>TC-SEL-248: Verify Dashboard - scenario 42</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>714</v>
+      </c>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>249</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>TC-SEL-249: Verify Checkout - scenario 42</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>142</v>
+      </c>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:57.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>250</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>TC-SEL-250: Verify Product Search - scenario 42</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1132</v>
+      </c>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:58.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>251</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>TC-SEL-251: Verify Settings - scenario 42</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>201</v>
+      </c>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:41:59.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>252</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>TC-SEL-252: Verify Registration - scenario 42</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>345</v>
+      </c>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:00.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>253</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>TC-SEL-253: Verify Login Flow - scenario 43</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>501</v>
+      </c>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>254</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>TC-SEL-254: Verify Dashboard - scenario 43</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>426</v>
+      </c>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:01.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>255</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>TC-SEL-255: Verify Checkout - scenario 43</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>1143</v>
+      </c>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:02.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>256</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>TC-SEL-256: Verify Product Search - scenario 43</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>787</v>
+      </c>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:03.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>257</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>TC-SEL-257: Verify Settings - scenario 43</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>1115</v>
+      </c>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:04.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>258</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>TC-SEL-258: Verify Registration - scenario 43</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>611</v>
+      </c>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>259</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>TC-SEL-259: Verify Login Flow - scenario 44</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>681</v>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:05.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>260</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>TC-SEL-260: Verify Dashboard - scenario 44</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>855</v>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:06.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>261</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>TC-SEL-261: Verify Checkout - scenario 44</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>884</v>
+      </c>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:07.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>262</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>TC-SEL-262: Verify Product Search - scenario 44</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>583</v>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:08.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>263</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>TC-SEL-263: Verify Settings - scenario 44</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>320</v>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>264</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>TC-SEL-264: Verify Registration - scenario 44</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>1101</v>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:09.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>265</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>TC-SEL-265: Verify Login Flow - scenario 45</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>914</v>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:10.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>266</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>TC-SEL-266: Verify Dashboard - scenario 45</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>519</v>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:11.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>267</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>TC-SEL-267: Verify Checkout - scenario 45</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>580</v>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:12.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>268</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>TC-SEL-268: Verify Product Search - scenario 45</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>923</v>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>269</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>TC-SEL-269: Verify Settings - scenario 45</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>582</v>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:13.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>270</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>TC-SEL-270: Verify Registration - scenario 45</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>674</v>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:14.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>271</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>TC-SEL-271: Verify Login Flow - scenario 46</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>920</v>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:15.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>272</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>TC-SEL-272: Verify Dashboard - scenario 46</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>200</v>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:16.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>273</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>TC-SEL-273: Verify Checkout - scenario 46</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>594</v>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>274</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>TC-SEL-274: Verify Product Search - scenario 46</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>1120</v>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:17.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>275</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>TC-SEL-275: Verify Settings - scenario 46</t>
+        </is>
+      </c>
+      <c r="D276" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>459</v>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:18.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>276</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>TC-SEL-276: Verify Registration - scenario 46</t>
+        </is>
+      </c>
+      <c r="D277" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>198</v>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:19.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>277</v>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>TC-SEL-277: Verify Login Flow - scenario 47</t>
+        </is>
+      </c>
+      <c r="D278" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>516</v>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:20.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>278</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>TC-SEL-278: Verify Dashboard - scenario 47</t>
+        </is>
+      </c>
+      <c r="D279" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>716</v>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>279</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>TC-SEL-279: Verify Checkout - scenario 47</t>
+        </is>
+      </c>
+      <c r="D280" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>958</v>
+      </c>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:21.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>280</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>TC-SEL-280: Verify Product Search - scenario 47</t>
+        </is>
+      </c>
+      <c r="D281" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>290</v>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:22.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>281</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>TC-SEL-281: Verify Settings - scenario 47</t>
+        </is>
+      </c>
+      <c r="D282" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>663</v>
+      </c>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:23.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>282</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>TC-SEL-282: Verify Registration - scenario 47</t>
+        </is>
+      </c>
+      <c r="D283" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>300</v>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:24.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>283</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>TC-SEL-283: Verify Login Flow - scenario 48</t>
+        </is>
+      </c>
+      <c r="D284" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>211</v>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>284</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>TC-SEL-284: Verify Dashboard - scenario 48</t>
+        </is>
+      </c>
+      <c r="D285" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>293</v>
+      </c>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:25.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>285</v>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>TC-SEL-285: Verify Checkout - scenario 48</t>
+        </is>
+      </c>
+      <c r="D286" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>164</v>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:26.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>286</v>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>TC-SEL-286: Verify Product Search - scenario 48</t>
+        </is>
+      </c>
+      <c r="D287" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>570</v>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:27.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>287</v>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>TC-SEL-287: Verify Settings - scenario 48</t>
+        </is>
+      </c>
+      <c r="D288" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>815</v>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:28.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>288</v>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>TC-SEL-288: Verify Registration - scenario 48</t>
+        </is>
+      </c>
+      <c r="D289" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>902</v>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>289</v>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>TC-SEL-289: Verify Login Flow - scenario 49</t>
+        </is>
+      </c>
+      <c r="D290" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>501</v>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:29.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>290</v>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>TC-SEL-290: Verify Dashboard - scenario 49</t>
+        </is>
+      </c>
+      <c r="D291" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>1165</v>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:30.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>291</v>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>TC-SEL-291: Verify Checkout - scenario 49</t>
+        </is>
+      </c>
+      <c r="D292" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>683</v>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:31.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>292</v>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>TC-SEL-292: Verify Product Search - scenario 49</t>
+        </is>
+      </c>
+      <c r="D293" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>1188</v>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:32.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>293</v>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>TC-SEL-293: Verify Settings - scenario 49</t>
+        </is>
+      </c>
+      <c r="D294" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>245</v>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>294</v>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>TC-SEL-294: Verify Registration - scenario 49</t>
+        </is>
+      </c>
+      <c r="D295" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>1063</v>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:33.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>295</v>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Login Flow</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>TC-SEL-295: Verify Login Flow - scenario 50</t>
+        </is>
+      </c>
+      <c r="D296" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>388</v>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:34.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>296</v>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Dashboard</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>TC-SEL-296: Verify Dashboard - scenario 50</t>
+        </is>
+      </c>
+      <c r="D297" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>456</v>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:35.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>297</v>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Checkout</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>TC-SEL-297: Verify Checkout - scenario 50</t>
+        </is>
+      </c>
+      <c r="D298" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>412</v>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:36.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="n">
+        <v>298</v>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Product Search</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>TC-SEL-298: Verify Product Search - scenario 50</t>
+        </is>
+      </c>
+      <c r="D299" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E299" t="n">
+        <v>924</v>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="n">
+        <v>299</v>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Settings</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>TC-SEL-299: Verify Settings - scenario 50</t>
+        </is>
+      </c>
+      <c r="D300" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E300" t="n">
+        <v>641</v>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:37.000Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="n">
+        <v>300</v>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Registration</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>TC-SEL-300: Verify Registration - scenario 50</t>
+        </is>
+      </c>
+      <c r="D301" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="E301" t="n">
+        <v>963</v>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>2026-08-05T17:42:38.000Z</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -567,7 +9325,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-08-05T17:36:39.000Z</t>
+          <t>2026-08-05T17:38:38.000Z</t>
         </is>
       </c>
     </row>
